--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202607/Currency_P&L_20260731.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202607/Currency_P&L_20260731.xlsx
@@ -1693,7 +1693,7 @@
         <v>46233</v>
       </c>
       <c r="B41">
-        <v>85859219.67</v>
+        <v>87859219.67</v>
       </c>
       <c r="C41">
         <v>30846.08</v>
@@ -1725,31 +1725,31 @@
         <v>46234</v>
       </c>
       <c r="B42">
-        <v>86263492.97</v>
+        <v>88263665.98999999</v>
       </c>
       <c r="C42">
         <v>-19784.59</v>
       </c>
       <c r="D42">
-        <v>-0.00023</v>
+        <v>-0.000225</v>
       </c>
       <c r="E42">
         <v>68001.59</v>
       </c>
       <c r="F42">
-        <v>0.000792</v>
+        <v>0.0007739999999999999</v>
       </c>
       <c r="G42">
         <v>-63561.88</v>
       </c>
       <c r="H42">
-        <v>-0.00074</v>
+        <v>-0.000723</v>
       </c>
       <c r="I42">
         <v>434413.15</v>
       </c>
       <c r="J42">
-        <v>0.00506</v>
+        <v>0.004944</v>
       </c>
     </row>
   </sheetData>
